--- a/src/excel/factura.xlsx
+++ b/src/excel/factura.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>PRÓXIMO VENCIMIENTO: 28/5/2026</t>
+    <t>PRÓXIMO VENCIMIENTO: 21/5/2026</t>
   </si>
   <si>
     <t>Incluye el valor de</t>

--- a/src/excel/factura.xlsx
+++ b/src/excel/factura.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>PRÓXIMO VENCIMIENTO: 21/5/2026</t>
+    <t>PRÓXIMO VENCIMIENTO: 19/5/2026</t>
   </si>
   <si>
     <t>Incluye el valor de</t>

--- a/src/excel/factura.xlsx
+++ b/src/excel/factura.xlsx
@@ -24,7 +24,7 @@
     <t>Las Margaritas</t>
   </si>
   <si>
-    <t>Fecha de pago:         17/5/2026</t>
+    <t>Fecha de pago:         18/5/2026</t>
   </si>
   <si>
     <t>Tristán Suárez</t>
@@ -33,13 +33,13 @@
     <t>Whatsapp: 1160344824</t>
   </si>
   <si>
-    <t>Número de Cuota:   1</t>
+    <t>Número de Cuota:   3</t>
   </si>
   <si>
     <t>COMPAÑÍA</t>
   </si>
   <si>
-    <t>atm</t>
+    <t>ATM</t>
   </si>
   <si>
     <t>ASEGURADO</t>
@@ -51,7 +51,7 @@
     <t>Número de póliza</t>
   </si>
   <si>
-    <t>111111</t>
+    <t>11112</t>
   </si>
   <si>
     <t>Automotor</t>
@@ -84,7 +84,7 @@
     <t>Otros</t>
   </si>
   <si>
-    <t>Uso particular</t>
+    <t>USO PARTICULAR</t>
   </si>
   <si>
     <t>IMPORTE: $  1</t>
@@ -93,13 +93,13 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>PRÓXIMO VENCIMIENTO: 19/5/2026</t>
+    <t>PRÓXIMO VENCIMIENTO: 31/5/2026</t>
   </si>
   <si>
     <t>Incluye el valor de</t>
   </si>
   <si>
-    <t/>
+    <t>6</t>
   </si>
   <si>
     <t>en concepto de servicios</t>
